--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_17_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_17_9.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9968366540679824</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7635031466242946</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9911897181088223</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9889897654985683</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9903886718552531</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02115330881327059</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.581455547491221</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01873522821738285</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02157317888825279</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0201542059213231</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1783681344143549</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1454417712119548</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000834289037016</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1516335285184194</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P2" t="n">
-        <v>237.7119178813084</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q2" t="n">
-        <v>377.8826377411515</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_1</t>
+          <t>model_17_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9972808941027176</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7631451926051862</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9929674035667985</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9876444750573447</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9906615394902567</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0181826736554589</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.583849187665225</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01495494704530607</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0242091074274135</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01958202376061588</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1685251575416866</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1348431446364957</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000717126830053</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1405836964674614</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P3" t="n">
-        <v>238.0145722705782</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q3" t="n">
-        <v>378.1852921304213</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_2</t>
+          <t>model_17_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9976143833324219</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7627601379009747</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9941136786443149</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9863062393539359</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9906175358681034</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0159526296408494</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.586424050245302</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01251737178466976</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02683121308924367</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01967429592621115</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1598999002614244</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1263037198219015</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000629173626614</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1316807306594637</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P4" t="n">
-        <v>238.2762631911513</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q4" t="n">
-        <v>378.4469830509943</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_3</t>
+          <t>model_17_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.997860822365949</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7623623872383949</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9947777716491931</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9850004238008104</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9903441965732588</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01430469068890683</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>1.589083810757446</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01110516566486106</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02938979551716338</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02024746712083942</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>0.152486096980227</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1196022185785315</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000564178716673</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1246939326341434</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P5" t="n">
-        <v>238.4943355505997</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q5" t="n">
-        <v>378.6650554104428</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_4</t>
+          <t>model_17_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9980391671280895</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7619627395525255</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9950776965029883</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9837445575926463</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9899095250978369</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01311209844327079</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.591756256673063</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01046736988791265</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03185050844429613</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02115893932237527</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.145809795174299</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1145080715201806</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000517142735449</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1193829171891803</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P6" t="n">
-        <v>238.6684398593855</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q6" t="n">
-        <v>378.8391597192286</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_5</t>
+          <t>model_17_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9981645042649619</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7615691182173318</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9951062775665699</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9825499201166161</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F7" t="n">
-        <v>0.989365877411109</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01227396843188038</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.594388404353964</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01040659172490828</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03419125132072271</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02229892614437912</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1398031025815903</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1107879435312362</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000484086787263</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O7" t="n">
-        <v>0.11550441565002</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P7" t="n">
-        <v>238.8005492939379</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q7" t="n">
-        <v>378.971269153781</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_6</t>
+          <t>model_17_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9982488595005171</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7611872678296918</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9949365608066473</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9814237668010097</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F8" t="n">
-        <v>0.988753669851505</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01170988458330294</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>1.596941839654372</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01076749756977668</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03639780804120084</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02358267767559624</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1343973787113083</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1082122201200167</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000461839252611</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1128190383607024</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P8" t="n">
-        <v>238.8946439153438</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q8" t="n">
-        <v>379.0653637751869</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_7</t>
+          <t>model_17_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9983017053317019</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7608210793711453</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9946252322026182</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E9" t="n">
-        <v>0.980368911225749</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9881029837941778</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01135650426683688</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>1.599390543562815</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0114295436335837</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03846466574740248</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02494711561715929</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1295304971184378</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1065669004280264</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N9" t="n">
-        <v>1.00044790189054</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1111036740031427</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P9" t="n">
-        <v>238.9559292720706</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q9" t="n">
-        <v>379.1266491319136</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_8</t>
+          <t>model_17_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9983306139593905</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C10" t="n">
-        <v>0.760473260783895</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9942167097990151</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9793870161193431</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9874371093442514</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01116319214037167</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>1.601716408057315</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01229827411893637</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04038856653055475</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02634340243407539</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1251521645026236</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1056560085388979</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000440277637084</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O10" t="n">
-        <v>0.110154003560488</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P10" t="n">
-        <v>238.9902666576909</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q10" t="n">
-        <v>379.160986517534</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_9</t>
+          <t>model_17_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9983415332474471</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7601453498110496</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9937449231817639</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9784771745275355</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9867727975379289</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01109017481085798</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.603909150242623</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01330153713064101</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04217128745420875</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02773641250916142</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1212080544478291</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1053098989215068</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000437397824849</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1097931593401388</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P11" t="n">
-        <v>239.0033914296346</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q11" t="n">
-        <v>379.1741112894777</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_10</t>
+          <t>model_17_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9983391090385938</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7598381373862301</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D12" t="n">
-        <v>0.993236025441246</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E12" t="n">
-        <v>0.97763705806374</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9861222528911674</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01110638550662316</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>1.605963481141974</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01438371763583678</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04381739070097129</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0291005539237912</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1176626074103206</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1053868374448307</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000438037176635</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1098733732956853</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P12" t="n">
-        <v>239.0004701304035</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q12" t="n">
-        <v>379.1711899902466</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_11</t>
+          <t>model_17_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9983270286103061</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7595518262717336</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9927096431123342</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9768642491511935</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9854942886585376</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01118716738620821</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>1.607878044882954</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01550307944327623</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04533161321045878</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03041734597011883</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1144687380897325</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1057694066647261</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000441223223655</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1102722292792991</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P13" t="n">
-        <v>238.9859758533297</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q13" t="n">
-        <v>379.1566957131728</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9983081359047901</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7592861250236721</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9921805082937761</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9761553175848326</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9848947513637462</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01131350299498665</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.609654790352183</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01662829447111515</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>0.04672067604092276</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03167452894366474</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1115935288293544</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1063649519107993</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N14" t="n">
-        <v>1.00044620591522</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1108931281194462</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P14" t="n">
-        <v>238.9635166226923</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q14" t="n">
-        <v>379.1342364825354</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_13</t>
+          <t>model_17_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9982846338427466</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7590405301564849</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9916594482551577</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9755063252411287</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9843273503679821</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01147066139208859</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>1.611297084359924</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01773633832930864</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04799229545338969</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03286432460315868</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1090063250378976</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1071011736261027</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000452404261254</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1116606923173591</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P15" t="n">
-        <v>238.9359253734462</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q15" t="n">
-        <v>379.1066452332893</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_14</t>
+          <t>model_17_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.998258228601641</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7588142776891617</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9911541397937721</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9749136361045625</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9837942279786958</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01164723336094639</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>1.612810035650711</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0188108861657081</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>0.04915359576598544</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03398224069686918</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1066785455462342</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1079223487556975</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000459368280886</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1125168265722876</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P16" t="n">
-        <v>238.9053732138406</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q16" t="n">
-        <v>379.0760930736837</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_15</t>
+          <t>model_17_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9982301933359228</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7586063063686213</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9906699565997961</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9743729972100924</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9832961200408789</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01183470531189503</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>1.614200740828785</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01984051072826011</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05021291013234472</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>0.03502673421520727</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.104583326613263</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1087874317735971</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000466762197119</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1134187379652279</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P17" t="n">
-        <v>238.8734378720787</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q17" t="n">
-        <v>379.0441577319218</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_16</t>
+          <t>model_17_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9982015147764665</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7584156751107992</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9902101498824568</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9738810250714953</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9828331401242106</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01202647897103152</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>1.615475492927617</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02081829826010535</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J18" t="n">
-        <v>0.05117686807098913</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03599756701140812</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1026984481625608</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1096653043174163</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N18" t="n">
-        <v>1.00047432577324</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1143339833606842</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P18" t="n">
-        <v>238.8412889583983</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q18" t="n">
-        <v>379.0120088182414</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_17</t>
+          <t>model_17_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9981729054966599</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7582412772218522</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9897771690345356</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9734335029479063</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9824044792449941</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01221778935683149</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.616641692414034</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02173904008196277</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0520537317588043</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03689643546122458</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1010017545984159</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1105341094722868</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000481871077804</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1152397753496722</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P19" t="n">
-        <v>238.8097244906</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q19" t="n">
-        <v>378.9804443504431</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_18</t>
+          <t>model_17_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9981449033329287</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7580820713555882</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9893717928074517</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9730271809587798</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9820091072398698</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01240503995464059</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.617706302774816</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02260108016446263</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0528498689306799</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03772549973692067</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09947352145908074</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1113779150219674</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000489256263843</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O20" t="n">
-        <v>0.116119503448521</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P20" t="n">
-        <v>238.7793048819877</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q20" t="n">
-        <v>378.9500247418308</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_19</t>
+          <t>model_17_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9981178625409954</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7579369235368287</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9889942954573473</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9726584643926797</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9816454492224282</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01258586185480959</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>1.618676906907206</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02340383529682056</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J21" t="n">
-        <v>0.053572322974552</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03848806225253532</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09809979996222623</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1121867276232335</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000496387901276</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1169627488766959</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P21" t="n">
-        <v>238.7503623400746</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q21" t="n">
-        <v>378.9210821999177</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_20</t>
+          <t>model_17_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9980920423510731</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7578047668217038</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9886440574285515</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9723244538485006</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9813117916668918</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0127585215837112</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>1.619560639469772</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02414862297568764</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0542267749046358</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0.03918771613805623</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>0.096863507865454</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1129536258103793</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000503197621695</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1177622955073666</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P22" t="n">
-        <v>238.7231117422474</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q22" t="n">
-        <v>378.8938316020905</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_21</t>
+          <t>model_17_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9980675894846697</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7576845728277616</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9883206144008386</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9720215406945468</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9810062781112456</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01292203801394645</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>1.620364377260706</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02483643058665523</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05482029538387737</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0398283542496176</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>0.09574835521772435</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1136751424628377</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000509646729318</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1185145286174655</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P23" t="n">
-        <v>238.6976421040999</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q23" t="n">
-        <v>378.868361963943</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_22</t>
+          <t>model_17_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9980446335016245</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7575754648656512</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9880227738816695</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9717479456559721</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9807274022149275</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01307554477827129</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>1.621093982705734</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02546979398727538</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05535637067903495</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.04041313526596034</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0.09474412322292776</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1143483483845363</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000515701054517</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1192163943089792</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P24" t="n">
-        <v>238.6740232085139</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q24" t="n">
-        <v>378.844743068357</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_17_9_23</t>
+          <t>model_17_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9980231655035127</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7574764454258016</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9877493027084374</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9714999192213327</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9804729045827701</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01321910138049642</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>1.621756126155951</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02605133552075432</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05584234748931953</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.04094679696263137</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.09384337372203086</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1149743509679286</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000521362944129</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1198690471183505</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P25" t="n">
-        <v>238.6521848422256</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q25" t="n">
-        <v>378.8229047020687</v>
+        <v>270.907218101667</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9980032148258522</v>
+        <v>0.9999833884608758</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7573866791009825</v>
+        <v>0.7026193746032225</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9874987086670457</v>
+        <v>0.9999986981081239</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9712760171729967</v>
+        <v>0.9999959795009445</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9802411973636922</v>
+        <v>0.9999983806777476</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01335251165387662</v>
+        <v>9.861327205304051e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>1.622356393983353</v>
+        <v>0.1765379854096545</v>
       </c>
       <c r="I26" t="n">
-        <v>0.02658422840810806</v>
+        <v>6.526907098259446e-07</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05628105557874058</v>
+        <v>1.373436607617627e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04143266893957644</v>
+        <v>1.013063658721786e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.09303018376938635</v>
+        <v>0.001096281391631049</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1155530685610582</v>
+        <v>0.003140275020647722</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000526624661314</v>
+        <v>1.000007522206396</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1204724019175302</v>
+        <v>0.00327396302954214</v>
       </c>
       <c r="P26" t="n">
-        <v>238.6321015459292</v>
+        <v>177.0537795868155</v>
       </c>
       <c r="Q26" t="n">
-        <v>378.8028214057723</v>
+        <v>270.907218101667</v>
       </c>
     </row>
   </sheetData>
